--- a/data/trans_orig/IP07A17-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07A17-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido hablar con todos sus amigos en 2007 (tasa de respuesta: 98,3%)</t>
+          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as, percibida por el adulto en 2007 (tasa de respuesta: 98,3%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22719</t>
+          <t>23285</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36217</t>
+          <t>35804</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30230</t>
+          <t>31226</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44615</t>
+          <t>45077</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57360</t>
+          <t>57604</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>76107</t>
+          <t>76255</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>53,47%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23954</t>
+          <t>24225</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37092</t>
+          <t>37138</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30821</t>
+          <t>29526</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45178</t>
+          <t>43983</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>58550</t>
+          <t>59278</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>77873</t>
+          <t>78022</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>54,71%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>724</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6901</t>
+          <t>6251</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10018</t>
+          <t>9559</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3982</t>
+          <t>4102</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13259</t>
+          <t>12807</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45454</t>
+          <t>46014</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61673</t>
+          <t>62347</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36674</t>
+          <t>36800</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52702</t>
+          <t>52703</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>87298</t>
+          <t>88191</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>109400</t>
+          <t>110917</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>54,95%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32247</t>
+          <t>32702</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47865</t>
+          <t>47885</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35570</t>
+          <t>36005</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51453</t>
+          <t>51297</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>73132</t>
+          <t>72730</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>94792</t>
+          <t>94136</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>46,64%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3676</t>
+          <t>3237</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11153</t>
+          <t>11947</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4534</t>
+          <t>4571</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13447</t>
+          <t>13321</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10019</t>
+          <t>10177</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>21979</t>
+          <t>22347</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,07%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>534</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4932</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4076</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>1218</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8034</t>
+          <t>7921</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3688</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3363</t>
+          <t>3340</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3965</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29163</t>
+          <t>28847</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40786</t>
+          <t>40588</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34113</t>
+          <t>33908</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>46069</t>
+          <t>46047</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,26%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>67024</t>
+          <t>67311</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>84036</t>
+          <t>83715</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>66,47%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13936</t>
+          <t>14326</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25335</t>
+          <t>25249</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14446</t>
+          <t>14582</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25942</t>
+          <t>26316</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>32240</t>
+          <t>32099</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48242</t>
+          <t>47526</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>37,74%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2938</t>
+          <t>2948</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10099</t>
+          <t>10127</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>2087</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8500</t>
+          <t>8694</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6035</t>
+          <t>6071</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15518</t>
+          <t>15213</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,08%</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3296</t>
+          <t>3735</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3534</t>
+          <t>3252</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31283</t>
+          <t>31280</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47397</t>
+          <t>47663</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35720</t>
+          <t>36509</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>52020</t>
+          <t>52602</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>73279</t>
+          <t>72833</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>95586</t>
+          <t>95062</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>50,88%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>29035</t>
+          <t>29112</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>45299</t>
+          <t>45556</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>33153</t>
+          <t>33459</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>49546</t>
+          <t>49573</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>51,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>67244</t>
+          <t>66173</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>89483</t>
+          <t>88675</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>47,46%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6658</t>
+          <t>6593</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17319</t>
+          <t>17141</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5942</t>
+          <t>5927</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15159</t>
+          <t>15929</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>15318</t>
+          <t>14899</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>29648</t>
+          <t>28690</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,36%</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5068</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5153</t>
+          <t>4720</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>690</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6379</t>
+          <t>6375</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4361</t>
+          <t>3928</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3911</t>
+          <t>4310</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>143677</t>
+          <t>143213</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>172006</t>
+          <t>171182</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>149801</t>
+          <t>152519</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>181093</t>
+          <t>182295</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>305050</t>
+          <t>304942</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>344854</t>
+          <t>344240</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>46,4%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>52,38%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>113145</t>
+          <t>113682</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>140461</t>
+          <t>141886</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>128459</t>
+          <t>127169</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>158308</t>
+          <t>157582</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>249463</t>
+          <t>248856</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>288571</t>
+          <t>289981</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>44,12%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>18702</t>
+          <t>18580</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>35177</t>
+          <t>34398</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>20323</t>
+          <t>20677</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>37004</t>
+          <t>36560</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>43777</t>
+          <t>43999</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>66166</t>
+          <t>66589</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7722</t>
+          <t>7328</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>683</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6831</t>
+          <t>6814</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2679</t>
+          <t>2693</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>10854</t>
+          <t>10641</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5058</t>
+          <t>4603</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4614</t>
+          <t>4544</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>776</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6885</t>
+          <t>7260</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido hablar con todos sus amigos en 2012 (tasa de respuesta: 97,39%)</t>
+          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as, percibida por el adulto en 2012 (tasa de respuesta: 97,39%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29596</t>
+          <t>30305</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43532</t>
+          <t>43445</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27443</t>
+          <t>27986</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41634</t>
+          <t>41995</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>62162</t>
+          <t>62018</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81962</t>
+          <t>80990</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>59,14%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17876</t>
+          <t>17429</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30665</t>
+          <t>30313</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24613</t>
+          <t>24127</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38335</t>
+          <t>38613</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45080</t>
+          <t>46736</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>64619</t>
+          <t>64805</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,32%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>661</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7023</t>
+          <t>6869</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3072</t>
+          <t>3224</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10858</t>
+          <t>10594</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4459</t>
+          <t>4800</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13918</t>
+          <t>14096</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6214</t>
+          <t>5884</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5532</t>
+          <t>5937</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42759</t>
+          <t>42526</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58660</t>
+          <t>58109</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42911</t>
+          <t>42942</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58328</t>
+          <t>58677</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>90707</t>
+          <t>90085</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>112319</t>
+          <t>111499</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>57,17%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35247</t>
+          <t>34810</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50857</t>
+          <t>50632</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32752</t>
+          <t>32260</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48136</t>
+          <t>47910</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>72427</t>
+          <t>72065</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>94038</t>
+          <t>93825</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>48,11%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>613</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5784</t>
+          <t>5877</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2261</t>
+          <t>2433</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10619</t>
+          <t>10758</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3945</t>
+          <t>3883</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13084</t>
+          <t>13199</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4588</t>
+          <t>4339</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3285</t>
+          <t>3095</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>609</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5454</t>
+          <t>5472</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4070</t>
+          <t>3811</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3442</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4610</t>
+          <t>4607</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27123</t>
+          <t>27356</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40231</t>
+          <t>39924</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38067</t>
+          <t>36927</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50435</t>
+          <t>49843</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>68299</t>
+          <t>69773</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>87204</t>
+          <t>87286</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>64,77%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16804</t>
+          <t>17220</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29559</t>
+          <t>29063</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13212</t>
+          <t>13312</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24670</t>
+          <t>25060</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>33938</t>
+          <t>33356</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51629</t>
+          <t>50584</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>37,54%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4459</t>
+          <t>4612</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13131</t>
+          <t>13727</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1492</t>
+          <t>1489</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7919</t>
+          <t>8055</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7516</t>
+          <t>7660</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17985</t>
+          <t>17705</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>591</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5835</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>580</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6109</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6195,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3683</t>
+          <t>3304</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>3318</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34297</t>
+          <t>34940</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>50804</t>
+          <t>50707</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40320</t>
+          <t>40552</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>55995</t>
+          <t>56341</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>60,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>79589</t>
+          <t>78612</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>102633</t>
+          <t>103649</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>56,73%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>28871</t>
+          <t>29471</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>45154</t>
+          <t>44954</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>27795</t>
+          <t>26143</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>43466</t>
+          <t>43192</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>59585</t>
+          <t>60226</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>82010</t>
+          <t>83829</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>45,88%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5177</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16716</t>
+          <t>16509</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3525</t>
+          <t>3489</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11768</t>
+          <t>12439</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10980</t>
+          <t>10824</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>24915</t>
+          <t>25383</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,89%</t>
         </is>
       </c>
     </row>
@@ -6764,7 +6764,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4294</t>
+          <t>3873</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>728</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6268</t>
+          <t>6890</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>763</t>
+          <t>772</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7483</t>
+          <t>7638</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3089</t>
+          <t>2998</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3326</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>149047</t>
+          <t>148993</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>178784</t>
+          <t>177753</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>163386</t>
+          <t>162006</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>193089</t>
+          <t>191181</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>320082</t>
+          <t>320716</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>363289</t>
+          <t>364353</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>56,1%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>112005</t>
+          <t>110896</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>141238</t>
+          <t>140418</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>108979</t>
+          <t>111806</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>138869</t>
+          <t>139177</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>232619</t>
+          <t>230053</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>271327</t>
+          <t>271028</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,73%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>15703</t>
+          <t>16158</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>32253</t>
+          <t>32227</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,7 +7343,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>15279</t>
+          <t>16184</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>31105</t>
+          <t>30314</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>35303</t>
+          <t>34678</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>57558</t>
+          <t>57100</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,79%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>8227</t>
+          <t>9142</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>2142</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>9312</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4679</t>
+          <t>4626</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>15194</t>
+          <t>15723</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>591</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>5173</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>646</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>5776</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido hablar con todos sus amigos en 2016 (tasa de respuesta: 97,64%)</t>
+          <t>Menores según la frecuencia de haber podido hablar de todo con sus amigos/as, percibida por el adulto en 2016 (tasa de respuesta: 97,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30574</t>
+          <t>31066</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45826</t>
+          <t>45062</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28738</t>
+          <t>29501</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43523</t>
+          <t>43970</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>64341</t>
+          <t>65668</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85299</t>
+          <t>85339</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>60,11%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21943</t>
+          <t>22101</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36994</t>
+          <t>36012</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21534</t>
+          <t>21706</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35810</t>
+          <t>35856</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>46104</t>
+          <t>47149</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>67000</t>
+          <t>66859</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,09%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>836</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7402</t>
+          <t>7157</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2916</t>
+          <t>2956</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11436</t>
+          <t>11117</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4755</t>
+          <t>4854</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15589</t>
+          <t>15438</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -8395,7 +8395,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4024</t>
+          <t>3592</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3865</t>
+          <t>3663</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8445,7 +8445,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47841</t>
+          <t>47998</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64405</t>
+          <t>63551</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49988</t>
+          <t>50496</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>67952</t>
+          <t>67747</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>103423</t>
+          <t>103792</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>126810</t>
+          <t>125810</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>59,71%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33353</t>
+          <t>33637</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49718</t>
+          <t>49514</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25954</t>
+          <t>25521</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41437</t>
+          <t>41177</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>63706</t>
+          <t>64324</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>85313</t>
+          <t>86276</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,95%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3708</t>
+          <t>3712</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11514</t>
+          <t>11100</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8944,7 +8944,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4039</t>
+          <t>4061</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12762</t>
+          <t>13191</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9333</t>
+          <t>8994</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>20849</t>
+          <t>20055</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -9042,7 +9042,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4931</t>
+          <t>5890</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>1366</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7830</t>
+          <t>7627</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9750</t>
+          <t>9802</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>661</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>5581</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>663</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5470</t>
+          <t>6035</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38560</t>
+          <t>38768</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>51423</t>
+          <t>51316</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40603</t>
+          <t>40744</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55128</t>
+          <t>55551</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>82930</t>
+          <t>83576</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>101712</t>
+          <t>103348</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>69,06%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15632</t>
+          <t>15948</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27591</t>
+          <t>28169</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16624</t>
+          <t>16509</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30433</t>
+          <t>30295</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36250</t>
+          <t>35975</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54142</t>
+          <t>54762</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,59%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>1548</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8835</t>
+          <t>8134</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2471</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9988</t>
+          <t>9662</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5644</t>
+          <t>5107</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14755</t>
+          <t>14578</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -9759,7 +9759,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4868</t>
+          <t>5544</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9794,7 +9794,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5011</t>
+          <t>5911</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9809,7 +9809,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -9837,7 +9837,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3274</t>
+          <t>3283</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3335</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>47995</t>
+          <t>49167</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>66025</t>
+          <t>67251</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48653</t>
+          <t>48331</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>64771</t>
+          <t>65069</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>101598</t>
+          <t>102272</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>126022</t>
+          <t>126416</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>61,52%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>28622</t>
+          <t>28635</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>45863</t>
+          <t>45274</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>25840</t>
+          <t>25794</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>41591</t>
+          <t>40830</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>59696</t>
+          <t>58680</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>82880</t>
+          <t>81732</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>39,78%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>3051</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13076</t>
+          <t>11515</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3622</t>
+          <t>4099</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12407</t>
+          <t>13282</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>9021</t>
+          <t>9034</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>21581</t>
+          <t>21914</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,67%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>735</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6946</t>
+          <t>7171</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3874</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10456,7 +10456,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1365</t>
+          <t>1385</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8276</t>
+          <t>7734</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>5028</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10534,7 +10534,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10554,7 +10554,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4999</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10569,7 +10569,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>723</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6969</t>
+          <t>6993</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>180801</t>
+          <t>181307</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>211375</t>
+          <t>211832</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>184981</t>
+          <t>185812</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>215282</t>
+          <t>216843</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>373874</t>
+          <t>373451</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>419120</t>
+          <t>420754</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>59,45%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>114830</t>
+          <t>116219</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>144470</t>
+          <t>145909</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>103881</t>
+          <t>102355</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>132224</t>
+          <t>130885</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>225974</t>
+          <t>224757</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>268154</t>
+          <t>269772</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>38,11%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>14437</t>
+          <t>14322</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>28560</t>
+          <t>28857</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>19079</t>
+          <t>18576</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>35387</t>
+          <t>35018</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>36872</t>
+          <t>37595</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>59589</t>
+          <t>59272</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1460</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9689</t>
+          <t>8701</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3063</t>
+          <t>3143</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>12664</t>
+          <t>11926</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>5894</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>17934</t>
+          <t>18016</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>656</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6584</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>7890</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2862</t>
+          <t>2921</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>11463</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
